--- a/auxiliary_data/Country_information.xlsx
+++ b/auxiliary_data/Country_information.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20410"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\meurerst\git\Anon-Lit-Review\eval_rev1\auxiliary_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\meurerst\git\anonymization-review\auxiliary_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534EF1C3-33BB-4898-B987-48C8624CB9F3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C7712C-6DE2-424B-85EF-5D687B51592A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28272" yWindow="5088" windowWidth="23832" windowHeight="15552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="150">
   <si>
     <t>EG</t>
   </si>
@@ -100,9 +100,6 @@
     <t>US</t>
   </si>
   <si>
-    <t>UK</t>
-  </si>
-  <si>
     <t>AT</t>
   </si>
   <si>
@@ -401,6 +398,81 @@
   </si>
   <si>
     <t>Low-income economies</t>
+  </si>
+  <si>
+    <t>GB</t>
+  </si>
+  <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>CO</t>
+  </si>
+  <si>
+    <t>CZ</t>
+  </si>
+  <si>
+    <t>GF</t>
+  </si>
+  <si>
+    <t>GH</t>
+  </si>
+  <si>
+    <t>HU</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>PE</t>
+  </si>
+  <si>
+    <t>PK</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>SR</t>
+  </si>
+  <si>
+    <t>ZW</t>
+  </si>
+  <si>
+    <t>United Arab Emirates</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>Czech Republic</t>
+  </si>
+  <si>
+    <t>French Guiana</t>
+  </si>
+  <si>
+    <t>Ghana</t>
+  </si>
+  <si>
+    <t>Hungary</t>
+  </si>
+  <si>
+    <t>Indonesia</t>
+  </si>
+  <si>
+    <t>Peru</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t>Qatar</t>
+  </si>
+  <si>
+    <t>Suriname</t>
+  </si>
+  <si>
+    <t>Zimbabwe</t>
   </si>
 </sst>
 </file>
@@ -748,7 +820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.5546875" customWidth="1"/>
@@ -758,22 +830,22 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1" t="s">
         <v>115</v>
       </c>
-      <c r="C1" t="s">
-        <v>116</v>
-      </c>
       <c r="D1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -781,10 +853,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D2" s="1">
         <v>26177414</v>
@@ -793,18 +865,18 @@
         <v>65099.845911898097</v>
       </c>
       <c r="F2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D3" s="1">
         <v>8939617</v>
@@ -813,18 +885,18 @@
         <v>52084.681195337202</v>
       </c>
       <c r="F3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D4" s="1">
         <v>171186373</v>
@@ -833,7 +905,7 @@
         <v>2688.3055009073801</v>
       </c>
       <c r="F4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -841,10 +913,10 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D5" s="1">
         <v>11655930</v>
@@ -853,18 +925,18 @@
         <v>49926.825429530501</v>
       </c>
       <c r="F5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D6" s="1">
         <v>215313498</v>
@@ -873,18 +945,18 @@
         <v>8917.6749105749495</v>
       </c>
       <c r="F6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D7" s="1">
         <v>6781953</v>
@@ -893,18 +965,18 @@
         <v>13974.449248779199</v>
       </c>
       <c r="F7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D8" s="1">
         <v>27914537</v>
@@ -913,7 +985,7 @@
         <v>1563.48894034459</v>
       </c>
       <c r="F8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -921,10 +993,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D9" s="1">
         <v>38454327</v>
@@ -933,18 +1005,18 @@
         <v>55522.445687687999</v>
       </c>
       <c r="F9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D10" s="1">
         <v>19603733</v>
@@ -953,7 +1025,7 @@
         <v>15355.4797401048</v>
       </c>
       <c r="F10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -961,10 +1033,10 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D11" s="1">
         <v>1433376202</v>
@@ -973,7 +1045,7 @@
         <v>12720.2163182</v>
       </c>
       <c r="F11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G11" s="1"/>
     </row>
@@ -982,10 +1054,10 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D12" s="1">
         <v>5882262</v>
@@ -994,7 +1066,7 @@
         <v>67790.053992327594</v>
       </c>
       <c r="F12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -1002,10 +1074,10 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D13" s="1">
         <v>110990103</v>
@@ -1014,18 +1086,18 @@
         <v>3886.7224983901001</v>
       </c>
       <c r="F13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D14" s="1">
         <v>1326062</v>
@@ -1034,18 +1106,18 @@
         <v>28247.095992497001</v>
       </c>
       <c r="F14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D15" s="1">
         <v>123379925</v>
@@ -1054,18 +1126,18 @@
         <v>1027.5859109596399</v>
       </c>
       <c r="F15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D16" s="1">
         <v>929766</v>
@@ -1074,7 +1146,7 @@
         <v>5356.1643962161397</v>
       </c>
       <c r="F16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1082,10 +1154,10 @@
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D17" s="1">
         <v>5540746</v>
@@ -1094,7 +1166,7 @@
         <v>50871.930450882101</v>
       </c>
       <c r="F17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1102,10 +1174,10 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D18" s="1">
         <v>64626628</v>
@@ -1114,18 +1186,18 @@
         <v>40886.2532680273</v>
       </c>
       <c r="F18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D19" s="1">
         <v>83369843</v>
@@ -1134,7 +1206,7 @@
         <v>48717.991140212798</v>
       </c>
       <c r="F19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1142,10 +1214,10 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D20" s="1">
         <v>1417173173</v>
@@ -1154,18 +1226,18 @@
         <v>2410.8880207068901</v>
       </c>
       <c r="F20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D21" s="1">
         <v>44496122</v>
@@ -1174,7 +1246,7 @@
         <v>5937.1954660027104</v>
       </c>
       <c r="F21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -1182,10 +1254,10 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D22" s="1">
         <v>5023109</v>
@@ -1194,18 +1266,18 @@
         <v>103983.29133582</v>
       </c>
       <c r="F22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D23" s="1">
         <v>9038309</v>
@@ -1214,7 +1286,7 @@
         <v>54930.938807509599</v>
       </c>
       <c r="F23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -1222,10 +1294,10 @@
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D24" s="1">
         <v>59037474</v>
@@ -1234,7 +1306,7 @@
         <v>34776.423234274</v>
       </c>
       <c r="F24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -1242,10 +1314,10 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D25" s="1">
         <v>123951692</v>
@@ -1254,18 +1326,18 @@
         <v>34017.271807502402</v>
       </c>
       <c r="F25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D26" s="1">
         <v>19397998</v>
@@ -1274,7 +1346,7 @@
         <v>11492.031938762</v>
       </c>
       <c r="F26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -1282,10 +1354,10 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D27" s="1">
         <v>54027487</v>
@@ -1294,18 +1366,18 @@
         <v>2099.30193826696</v>
       </c>
       <c r="F27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="1">
         <v>5489740</v>
@@ -1314,18 +1386,18 @@
         <v>4136.1465751601299</v>
       </c>
       <c r="F28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D29" s="1">
         <v>5302681</v>
@@ -1334,18 +1406,18 @@
         <v>754.53284291474404</v>
       </c>
       <c r="F29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D30" s="1">
         <v>33938222</v>
@@ -1354,18 +1426,18 @@
         <v>11993.1876132994</v>
       </c>
       <c r="F30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D31" s="1">
         <v>521021</v>
@@ -1374,18 +1446,18 @@
         <v>11780.8169102421</v>
       </c>
       <c r="F31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D32" s="1">
         <v>30547580</v>
@@ -1394,18 +1466,18 @@
         <v>1336.5460472984701</v>
       </c>
       <c r="F32" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D33" s="1">
         <v>17564014</v>
@@ -1414,7 +1486,7 @@
         <v>57025.012455980002</v>
       </c>
       <c r="F33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1422,10 +1494,10 @@
         <v>18</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D34" s="1">
         <v>5185289</v>
@@ -1434,7 +1506,7 @@
         <v>48418.5916631992</v>
       </c>
       <c r="F34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -1442,10 +1514,10 @@
         <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D35" s="1">
         <v>218541212</v>
@@ -1454,18 +1526,18 @@
         <v>2162.6337342857701</v>
       </c>
       <c r="F35" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C36" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D36" s="1">
         <v>5434319</v>
@@ -1474,7 +1546,7 @@
         <v>108729.18690323</v>
       </c>
       <c r="F36" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -1482,10 +1554,10 @@
         <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D37" s="1">
         <v>39857146</v>
@@ -1494,18 +1566,18 @@
         <v>18688.004486710299</v>
       </c>
       <c r="F37" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D38" s="1">
         <v>10270865</v>
@@ -1514,7 +1586,7 @@
         <v>24515.265850731899</v>
       </c>
       <c r="F38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -1522,10 +1594,10 @@
         <v>19</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D39" s="1">
         <v>19659267</v>
@@ -1534,18 +1606,18 @@
         <v>15786.8017421977</v>
       </c>
       <c r="F39" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B40" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" t="s">
         <v>119</v>
-      </c>
-      <c r="C40" t="s">
-        <v>120</v>
       </c>
       <c r="D40" s="1">
         <v>144713314</v>
@@ -1554,7 +1626,7 @@
         <v>15270.7060546875</v>
       </c>
       <c r="F40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -1562,10 +1634,10 @@
         <v>16</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C41" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D41" s="1">
         <v>36408820</v>
@@ -1574,18 +1646,18 @@
         <v>30447.883707447301</v>
       </c>
       <c r="F41" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C42" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D42" s="1">
         <v>8605718</v>
@@ -1594,7 +1666,7 @@
         <v>475.79572784462198</v>
       </c>
       <c r="F42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -1602,10 +1674,10 @@
         <v>21</v>
       </c>
       <c r="B43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D43" s="1">
         <v>5975689</v>
@@ -1614,7 +1686,7 @@
         <v>82807.629062289707</v>
       </c>
       <c r="F43" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -1622,10 +1694,10 @@
         <v>5</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D44" s="1">
         <v>59893886</v>
@@ -1634,7 +1706,7 @@
         <v>6766.4812542947802</v>
       </c>
       <c r="F44" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -1642,10 +1714,10 @@
         <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C45" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D45" s="1">
         <v>51815810</v>
@@ -1654,7 +1726,7 @@
         <v>35142.264267480998</v>
       </c>
       <c r="F45" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -1662,10 +1734,10 @@
         <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D46" s="1">
         <v>47558630</v>
@@ -1674,18 +1746,18 @@
         <v>29674.544286441302</v>
       </c>
       <c r="F46" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C47" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D47" s="1">
         <v>10549347</v>
@@ -1694,7 +1766,7 @@
         <v>56424.284698668598</v>
       </c>
       <c r="F47" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -1702,10 +1774,10 @@
         <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C48" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D48" s="1">
         <v>8740472</v>
@@ -1714,7 +1786,7 @@
         <v>93259.905718302398</v>
       </c>
       <c r="F48" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -1722,10 +1794,10 @@
         <v>6</v>
       </c>
       <c r="B49" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C49" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D49" s="1">
         <v>23893395</v>
@@ -1734,18 +1806,18 @@
         <v>34432</v>
       </c>
       <c r="F49" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B50" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D50" s="1">
         <v>71697030</v>
@@ -1754,18 +1826,18 @@
         <v>6909.9562847948</v>
       </c>
       <c r="F50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D51" s="1">
         <v>1531045</v>
@@ -1774,18 +1846,18 @@
         <v>19629.465340082901</v>
       </c>
       <c r="F51" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C52" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D52" s="1">
         <v>85341241</v>
@@ -1794,18 +1866,18 @@
         <v>10674.5041731531</v>
       </c>
       <c r="F52" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="B53" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C53" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D53" s="1">
         <v>67508936</v>
@@ -1814,7 +1886,7 @@
         <v>46125.255751356803</v>
       </c>
       <c r="F53" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -1822,10 +1894,10 @@
         <v>24</v>
       </c>
       <c r="B54" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C54" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D54" s="1">
         <v>338289857</v>
@@ -1834,7 +1906,139 @@
         <v>76329.582265202902</v>
       </c>
       <c r="F54" t="s">
-        <v>122</v>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>126</v>
+      </c>
+      <c r="B55" t="s">
+        <v>138</v>
+      </c>
+      <c r="C55" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" t="s">
+        <v>139</v>
+      </c>
+      <c r="C56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>128</v>
+      </c>
+      <c r="B57" t="s">
+        <v>140</v>
+      </c>
+      <c r="C57" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>129</v>
+      </c>
+      <c r="B58" t="s">
+        <v>141</v>
+      </c>
+      <c r="C58" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>130</v>
+      </c>
+      <c r="B59" t="s">
+        <v>142</v>
+      </c>
+      <c r="C59" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>131</v>
+      </c>
+      <c r="B60" t="s">
+        <v>143</v>
+      </c>
+      <c r="C60" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>132</v>
+      </c>
+      <c r="B61" t="s">
+        <v>144</v>
+      </c>
+      <c r="C61" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>133</v>
+      </c>
+      <c r="B62" t="s">
+        <v>145</v>
+      </c>
+      <c r="C62" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>134</v>
+      </c>
+      <c r="B63" t="s">
+        <v>146</v>
+      </c>
+      <c r="C63" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>135</v>
+      </c>
+      <c r="B64" t="s">
+        <v>147</v>
+      </c>
+      <c r="C64" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>136</v>
+      </c>
+      <c r="B65" t="s">
+        <v>148</v>
+      </c>
+      <c r="C65" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>137</v>
+      </c>
+      <c r="B66" t="s">
+        <v>149</v>
+      </c>
+      <c r="C66" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/auxiliary_data/Country_information.xlsx
+++ b/auxiliary_data/Country_information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\meurerst\git\anonymization-review\auxiliary_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C7712C-6DE2-424B-85EF-5D687B51592A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD7B06D-3445-4AAC-9BFE-DF9A467844F1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28272" yWindow="5088" windowWidth="23832" windowHeight="15552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="148">
   <si>
     <t>EG</t>
   </si>
@@ -340,9 +340,6 @@
     <t>Country</t>
   </si>
   <si>
-    <t>European Union</t>
-  </si>
-  <si>
     <t>Core Anglosphere</t>
   </si>
   <si>
@@ -361,12 +358,6 @@
     <t>Oceania</t>
   </si>
   <si>
-    <t>Europe</t>
-  </si>
-  <si>
-    <t>Caribbean</t>
-  </si>
-  <si>
     <t>Name (Country)</t>
   </si>
   <si>
@@ -473,6 +464,9 @@
   </si>
   <si>
     <t>Zimbabwe</t>
+  </si>
+  <si>
+    <t>Continental Europe</t>
   </si>
 </sst>
 </file>
@@ -824,6 +818,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.5546875" customWidth="1"/>
+    <col min="3" max="3" width="34.44140625" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -833,1132 +828,1114 @@
         <v>104</v>
       </c>
       <c r="B1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D1" t="s">
         <v>103</v>
       </c>
       <c r="E1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1" t="s">
         <v>117</v>
-      </c>
-      <c r="F1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
         <v>106</v>
       </c>
       <c r="D2" s="1">
-        <v>26177414</v>
+        <v>171186373</v>
       </c>
       <c r="E2">
-        <v>65099.845911898097</v>
+        <v>2688.3055009073801</v>
       </c>
       <c r="F2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D3" s="1">
-        <v>8939617</v>
-      </c>
-      <c r="E3">
-        <v>52084.681195337202</v>
+        <v>1433376202</v>
+      </c>
+      <c r="E3" s="1">
+        <v>12720.2163182</v>
       </c>
       <c r="F3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D4" s="1">
-        <v>171186373</v>
+        <v>1417173173</v>
       </c>
       <c r="E4">
-        <v>2688.3055009073801</v>
+        <v>2410.8880207068901</v>
       </c>
       <c r="F4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D5" s="1">
-        <v>11655930</v>
+        <v>44496122</v>
       </c>
       <c r="E5">
-        <v>49926.825429530501</v>
+        <v>5937.1954660027104</v>
       </c>
       <c r="F5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D6" s="1">
-        <v>215313498</v>
+        <v>9038309</v>
       </c>
       <c r="E6">
-        <v>8917.6749105749495</v>
+        <v>54930.938807509599</v>
       </c>
       <c r="F6" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D7" s="1">
-        <v>6781953</v>
+        <v>123951692</v>
       </c>
       <c r="E7">
-        <v>13974.449248779199</v>
+        <v>34017.271807502402</v>
       </c>
       <c r="F7" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="D8" s="1">
-        <v>27914537</v>
+        <v>19397998</v>
       </c>
       <c r="E8">
-        <v>1563.48894034459</v>
+        <v>11492.031938762</v>
       </c>
       <c r="F8" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
         <v>106</v>
       </c>
       <c r="D9" s="1">
-        <v>38454327</v>
+        <v>5489740</v>
       </c>
       <c r="E9">
-        <v>55522.445687687999</v>
+        <v>4136.1465751601299</v>
       </c>
       <c r="F9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D10" s="1">
-        <v>19603733</v>
+        <v>33938222</v>
       </c>
       <c r="E10">
-        <v>15355.4797401048</v>
+        <v>11993.1876132994</v>
       </c>
       <c r="F10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D11" s="1">
-        <v>1433376202</v>
-      </c>
-      <c r="E11" s="1">
-        <v>12720.2163182</v>
+        <v>521021</v>
+      </c>
+      <c r="E11">
+        <v>11780.8169102421</v>
       </c>
       <c r="F11" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D12" s="1">
-        <v>5882262</v>
+        <v>30547580</v>
       </c>
       <c r="E12">
-        <v>67790.053992327594</v>
+        <v>1336.5460472984701</v>
       </c>
       <c r="F12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D13" s="1">
-        <v>110990103</v>
+        <v>36408820</v>
       </c>
       <c r="E13">
-        <v>3886.7224983901001</v>
+        <v>30447.883707447301</v>
       </c>
       <c r="F13" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D14" s="1">
-        <v>1326062</v>
+        <v>5975689</v>
       </c>
       <c r="E14">
-        <v>28247.095992497001</v>
+        <v>82807.629062289707</v>
       </c>
       <c r="F14" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D15" s="1">
-        <v>123379925</v>
+        <v>51815810</v>
       </c>
       <c r="E15">
-        <v>1027.5859109596399</v>
+        <v>35142.264267480998</v>
       </c>
       <c r="F15" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D16" s="1">
-        <v>929766</v>
+        <v>23893395</v>
       </c>
       <c r="E16">
-        <v>5356.1643962161397</v>
+        <v>34432</v>
       </c>
       <c r="F16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D17" s="1">
-        <v>5540746</v>
+        <v>71697030</v>
       </c>
       <c r="E17">
-        <v>50871.930450882101</v>
+        <v>6909.9562847948</v>
       </c>
       <c r="F17" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D18" s="1">
-        <v>64626628</v>
+        <v>85341241</v>
       </c>
       <c r="E18">
-        <v>40886.2532680273</v>
+        <v>10674.5041731531</v>
       </c>
       <c r="F18" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>135</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" s="1">
-        <v>83369843</v>
-      </c>
-      <c r="E19">
-        <v>48717.991140212798</v>
-      </c>
-      <c r="F19" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="B20" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
-      </c>
-      <c r="D20" s="1">
-        <v>1417173173</v>
-      </c>
-      <c r="E20">
-        <v>2410.8880207068901</v>
-      </c>
-      <c r="F20" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>131</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>143</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" s="1">
-        <v>44496122</v>
-      </c>
-      <c r="E21">
-        <v>5937.1954660027104</v>
-      </c>
-      <c r="F21" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>132</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D22" s="1">
-        <v>5023109</v>
-      </c>
-      <c r="E22">
-        <v>103983.29133582</v>
-      </c>
-      <c r="F22" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C23" t="s">
         <v>107</v>
       </c>
       <c r="D23" s="1">
-        <v>9038309</v>
+        <v>1531045</v>
       </c>
       <c r="E23">
-        <v>54930.938807509599</v>
+        <v>19629.465340082901</v>
       </c>
       <c r="F23" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24" t="s">
         <v>105</v>
       </c>
       <c r="D24" s="1">
-        <v>59037474</v>
+        <v>26177414</v>
       </c>
       <c r="E24">
-        <v>34776.423234274</v>
+        <v>65099.845911898097</v>
       </c>
       <c r="F24" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D25" s="1">
-        <v>123951692</v>
+        <v>38454327</v>
       </c>
       <c r="E25">
-        <v>34017.271807502402</v>
+        <v>55522.445687687999</v>
       </c>
       <c r="F25" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>79</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D26" s="1">
-        <v>19397998</v>
+        <v>5185289</v>
       </c>
       <c r="E26">
-        <v>11492.031938762</v>
+        <v>48418.5916631992</v>
       </c>
       <c r="F26" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="D27" s="1">
-        <v>54027487</v>
+        <v>67508936</v>
       </c>
       <c r="E27">
-        <v>2099.30193826696</v>
+        <v>46125.255751356803</v>
       </c>
       <c r="F27" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D28" s="1">
-        <v>5489740</v>
+        <v>338289857</v>
       </c>
       <c r="E28">
-        <v>4136.1465751601299</v>
+        <v>76329.582265202902</v>
       </c>
       <c r="F28" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="D29" s="1">
-        <v>5302681</v>
+        <v>123379925</v>
       </c>
       <c r="E29">
-        <v>754.53284291474404</v>
+        <v>1027.5859109596399</v>
       </c>
       <c r="F29" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D30" s="1">
-        <v>33938222</v>
+        <v>144713314</v>
       </c>
       <c r="E30">
-        <v>11993.1876132994</v>
+        <v>15270.7060546875</v>
       </c>
       <c r="F30" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="D31" s="1">
-        <v>521021</v>
+        <v>5434319</v>
       </c>
       <c r="E31">
-        <v>11780.8169102421</v>
+        <v>108729.18690323</v>
       </c>
       <c r="F31" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="D32" s="1">
-        <v>30547580</v>
+        <v>8740472</v>
       </c>
       <c r="E32">
-        <v>1336.5460472984701</v>
+        <v>93259.905718302398</v>
       </c>
       <c r="F32" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>147</v>
       </c>
       <c r="D33" s="1">
-        <v>17564014</v>
+        <v>8939617</v>
       </c>
       <c r="E33">
-        <v>57025.012455980002</v>
+        <v>52084.681195337202</v>
       </c>
       <c r="F33" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="D34" s="1">
-        <v>5185289</v>
+        <v>11655930</v>
       </c>
       <c r="E34">
-        <v>48418.5916631992</v>
+        <v>49926.825429530501</v>
       </c>
       <c r="F34" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="C35" t="s">
-        <v>56</v>
+        <v>147</v>
       </c>
       <c r="D35" s="1">
-        <v>218541212</v>
+        <v>6781953</v>
       </c>
       <c r="E35">
-        <v>2162.6337342857701</v>
+        <v>13974.449248779199</v>
       </c>
       <c r="F35" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="B36" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="D36" s="1">
-        <v>5434319</v>
+        <v>5882262</v>
       </c>
       <c r="E36">
-        <v>108729.18690323</v>
+        <v>67790.053992327594</v>
       </c>
       <c r="F36" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>147</v>
       </c>
       <c r="D37" s="1">
-        <v>39857146</v>
+        <v>1326062</v>
       </c>
       <c r="E37">
-        <v>18688.004486710299</v>
+        <v>28247.095992497001</v>
       </c>
       <c r="F37" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="B38" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="C38" t="s">
-        <v>105</v>
+        <v>147</v>
       </c>
       <c r="D38" s="1">
-        <v>10270865</v>
+        <v>5540746</v>
       </c>
       <c r="E38">
-        <v>24515.265850731899</v>
+        <v>50871.930450882101</v>
       </c>
       <c r="F38" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C39" t="s">
-        <v>105</v>
+        <v>147</v>
       </c>
       <c r="D39" s="1">
-        <v>19659267</v>
+        <v>64626628</v>
       </c>
       <c r="E39">
-        <v>15786.8017421977</v>
+        <v>40886.2532680273</v>
       </c>
       <c r="F39" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="C40" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="D40" s="1">
-        <v>144713314</v>
+        <v>83369843</v>
       </c>
       <c r="E40">
-        <v>15270.7060546875</v>
+        <v>48717.991140212798</v>
       </c>
       <c r="F40" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B41" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C41" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D41" s="1">
-        <v>36408820</v>
+        <v>5023109</v>
       </c>
       <c r="E41">
-        <v>30447.883707447301</v>
+        <v>103983.29133582</v>
       </c>
       <c r="F41" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="C42" t="s">
-        <v>56</v>
+        <v>147</v>
       </c>
       <c r="D42" s="1">
-        <v>8605718</v>
+        <v>59037474</v>
       </c>
       <c r="E42">
-        <v>475.79572784462198</v>
+        <v>34776.423234274</v>
       </c>
       <c r="F42" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C43" t="s">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="D43" s="1">
-        <v>5975689</v>
+        <v>17564014</v>
       </c>
       <c r="E43">
-        <v>82807.629062289707</v>
+        <v>57025.012455980002</v>
       </c>
       <c r="F43" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="C44" t="s">
-        <v>56</v>
+        <v>147</v>
       </c>
       <c r="D44" s="1">
-        <v>59893886</v>
+        <v>39857146</v>
       </c>
       <c r="E44">
-        <v>6766.4812542947802</v>
+        <v>18688.004486710299</v>
       </c>
       <c r="F44" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="C45" t="s">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="D45" s="1">
-        <v>51815810</v>
+        <v>10270865</v>
       </c>
       <c r="E45">
-        <v>35142.264267480998</v>
+        <v>24515.265850731899</v>
       </c>
       <c r="F45" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B46" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C46" t="s">
-        <v>105</v>
+        <v>147</v>
       </c>
       <c r="D46" s="1">
-        <v>47558630</v>
+        <v>19659267</v>
       </c>
       <c r="E46">
-        <v>29674.544286441302</v>
+        <v>15786.8017421977</v>
       </c>
       <c r="F46" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B47" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C47" t="s">
-        <v>105</v>
+        <v>147</v>
       </c>
       <c r="D47" s="1">
-        <v>10549347</v>
+        <v>47558630</v>
       </c>
       <c r="E47">
-        <v>56424.284698668598</v>
+        <v>29674.544286441302</v>
       </c>
       <c r="F47" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B48" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C48" t="s">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="D48" s="1">
-        <v>8740472</v>
+        <v>10549347</v>
       </c>
       <c r="E48">
-        <v>93259.905718302398</v>
+        <v>56424.284698668598</v>
       </c>
       <c r="F48" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>6</v>
+        <v>125</v>
       </c>
       <c r="B49" t="s">
-        <v>33</v>
+        <v>137</v>
       </c>
       <c r="C49" t="s">
-        <v>107</v>
-      </c>
-      <c r="D49" s="1">
-        <v>23893395</v>
-      </c>
-      <c r="E49">
-        <v>34432</v>
-      </c>
-      <c r="F49" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>61</v>
+        <v>128</v>
       </c>
       <c r="B50" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="C50" t="s">
-        <v>107</v>
-      </c>
-      <c r="D50" s="1">
-        <v>71697030</v>
-      </c>
-      <c r="E50">
-        <v>6909.9562847948</v>
-      </c>
-      <c r="F50" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>29</v>
       </c>
       <c r="C51" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D51" s="1">
-        <v>1531045</v>
+        <v>110990103</v>
       </c>
       <c r="E51">
-        <v>19629.465340082901</v>
+        <v>3886.7224983901001</v>
       </c>
       <c r="F51" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="C52" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D52" s="1">
-        <v>85341241</v>
+        <v>929766</v>
       </c>
       <c r="E52">
-        <v>10674.5041731531</v>
+        <v>5356.1643962161397</v>
       </c>
       <c r="F52" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>125</v>
+        <v>67</v>
       </c>
       <c r="B53" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="C53" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="D53" s="1">
-        <v>67508936</v>
+        <v>27914537</v>
       </c>
       <c r="E53">
-        <v>46125.255751356803</v>
+        <v>1563.48894034459</v>
       </c>
       <c r="F53" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B54" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C54" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="D54" s="1">
-        <v>338289857</v>
+        <v>54027487</v>
       </c>
       <c r="E54">
-        <v>76329.582265202902</v>
+        <v>2099.30193826696</v>
       </c>
       <c r="F54" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>126</v>
+        <v>69</v>
       </c>
       <c r="B55" t="s">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="C55" t="s">
-        <v>107</v>
+        <v>56</v>
+      </c>
+      <c r="D55" s="1">
+        <v>5302681</v>
+      </c>
+      <c r="E55">
+        <v>754.53284291474404</v>
+      </c>
+      <c r="F55" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>127</v>
+        <v>23</v>
       </c>
       <c r="B56" t="s">
-        <v>139</v>
+        <v>49</v>
       </c>
       <c r="C56" t="s">
-        <v>108</v>
+        <v>56</v>
+      </c>
+      <c r="D56" s="1">
+        <v>218541212</v>
+      </c>
+      <c r="E56">
+        <v>2162.6337342857701</v>
+      </c>
+      <c r="F56" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="C57" t="s">
-        <v>105</v>
+        <v>56</v>
+      </c>
+      <c r="D57" s="1">
+        <v>8605718</v>
+      </c>
+      <c r="E57">
+        <v>475.79572784462198</v>
+      </c>
+      <c r="F57" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>129</v>
+        <v>5</v>
       </c>
       <c r="B58" t="s">
-        <v>141</v>
+        <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>108</v>
+        <v>56</v>
+      </c>
+      <c r="D58" s="1">
+        <v>59893886</v>
+      </c>
+      <c r="E58">
+        <v>6766.4812542947802</v>
+      </c>
+      <c r="F58" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B59" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C59" t="s">
         <v>56</v>
@@ -1966,43 +1943,61 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B60" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C60" t="s">
-        <v>105</v>
+        <v>56</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="B61" t="s">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="C61" t="s">
         <v>107</v>
       </c>
+      <c r="D61" s="1">
+        <v>215313498</v>
+      </c>
+      <c r="E61">
+        <v>8917.6749105749495</v>
+      </c>
+      <c r="F61" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="B62" t="s">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="C62" t="s">
-        <v>108</v>
+        <v>107</v>
+      </c>
+      <c r="D62" s="1">
+        <v>19603733</v>
+      </c>
+      <c r="E62">
+        <v>15355.4797401048</v>
+      </c>
+      <c r="F62" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B63" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C63" t="s">
         <v>107</v>
@@ -2010,10 +2005,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="B64" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C64" t="s">
         <v>107</v>
@@ -2021,30 +2016,30 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B65" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C65" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B66" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C66" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G54" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <sortState ref="A2:E54">
-    <sortCondition ref="B1:B54"/>
+  <sortState ref="A2:F66">
+    <sortCondition ref="C1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/auxiliary_data/Country_information.xlsx
+++ b/auxiliary_data/Country_information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\meurerst\git\anonymization-review\auxiliary_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD7B06D-3445-4AAC-9BFE-DF9A467844F1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55C11FC8-5EA4-49FA-852F-427829BAC3D8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28272" yWindow="5088" windowWidth="23832" windowHeight="15552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Country_information" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Country_information!$A$1:$G$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Country_information!$A$1:$G$66</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="148">
   <si>
     <t>EG</t>
   </si>
@@ -1194,6 +1194,9 @@
       <c r="C19" t="s">
         <v>106</v>
       </c>
+      <c r="F19" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -1205,6 +1208,9 @@
       <c r="C20" t="s">
         <v>106</v>
       </c>
+      <c r="F20" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
@@ -1216,6 +1222,9 @@
       <c r="C21" t="s">
         <v>106</v>
       </c>
+      <c r="F21" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -1227,6 +1236,9 @@
       <c r="C22" t="s">
         <v>106</v>
       </c>
+      <c r="F22" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
@@ -1758,6 +1770,9 @@
       <c r="C49" t="s">
         <v>147</v>
       </c>
+      <c r="F49" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
@@ -1769,6 +1784,9 @@
       <c r="C50" t="s">
         <v>147</v>
       </c>
+      <c r="F50" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
@@ -1940,6 +1958,9 @@
       <c r="C59" t="s">
         <v>56</v>
       </c>
+      <c r="F59" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
@@ -1951,6 +1972,9 @@
       <c r="C60" t="s">
         <v>56</v>
       </c>
+      <c r="F60" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
@@ -2002,6 +2026,9 @@
       <c r="C63" t="s">
         <v>107</v>
       </c>
+      <c r="F63" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
@@ -2013,8 +2040,11 @@
       <c r="C64" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F64" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>130</v>
       </c>
@@ -2024,8 +2054,11 @@
       <c r="C65" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F65" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>133</v>
       </c>
@@ -2035,9 +2068,12 @@
       <c r="C66" t="s">
         <v>107</v>
       </c>
+      <c r="F66" t="s">
+        <v>119</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G54" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G66" xr:uid="{66F99AA2-F599-4B8A-851F-C3679087915D}"/>
   <sortState ref="A2:F66">
     <sortCondition ref="C1"/>
   </sortState>
